--- a/overlap_table.xlsx
+++ b/overlap_table.xlsx
@@ -587,17 +587,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -625,7 +625,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>3074</v>
+        <v>2709</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -636,17 +636,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>3074</v>
+        <v>2709</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
@@ -685,17 +685,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2709</v>
+        <v>3074</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -734,17 +734,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2709</v>
+        <v>3074</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -783,17 +783,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>517</v>
+        <v>152</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -870,28 +870,28 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>152</v>
+        <v>517</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3652</v>
+        <v>3287</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3287</v>
+        <v>3652</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -979,17 +979,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6810 O</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2485</v>
+        <v>1979</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1028,17 +1028,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6810 O</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2485</v>
+        <v>1979</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1077,17 +1077,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1979</v>
+        <v>2485</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1979</v>
+        <v>2485</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1175,17 +1175,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6810 O</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3063</v>
+        <v>2557</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1224,17 +1224,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>2557</v>
+        <v>3063</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>

--- a/overlap_table.xlsx
+++ b/overlap_table.xlsx
@@ -413,11 +413,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="59" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="60" customWidth="1" min="5" max="5"/>
@@ -587,12 +587,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>06367 D - G</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -601,31 +601,31 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20793</v>
+        <v>20989</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
+          <t>SAV: RICE HOPE NEW AUTO TRANSFORMER</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2033-06-01</t>
+          <t>2029-06-01</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>11.074</v>
+        <v>5.565</v>
       </c>
       <c r="H4" t="n">
-        <v>6.88</v>
+        <v>3.46</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Under 40 km -- can share crews &amp; equipment</t>
+          <t>Under 8 km -- can share site logistics (laydown yards, deliveries)</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2709</v>
+        <v>1248</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -650,11 +650,11 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>20794</v>
+        <v>20793</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -685,25 +685,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>20793</v>
+        <v>20794</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>3074</v>
+        <v>2709</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
@@ -748,11 +748,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20794</v>
+        <v>20793</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -783,37 +783,37 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16007</v>
+        <v>20794</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>FENWICK STREET - SAND BAR FERRY 115KV (RECONDUCTOR/REBUILD)</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2033-06-01</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>15.183</v>
+        <v>11.074</v>
       </c>
       <c r="H8" t="n">
-        <v>9.43</v>
+        <v>6.88</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -821,28 +821,28 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>152</v>
+        <v>3074</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -870,48 +870,48 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>517</v>
+        <v>152</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>6809 G</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17993</v>
+        <v>16007</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
+          <t>FENWICK STREET - SAND BAR FERRY 115KV (RECONDUCTOR/REBUILD)</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2034-12-31</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>23.362</v>
+        <v>15.183</v>
       </c>
       <c r="H10" t="n">
-        <v>14.52</v>
+        <v>9.43</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>3287</v>
+        <v>517</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -930,17 +930,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>6809 E</t>
+          <t>6809 G</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2024-12-31</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>3652</v>
+        <v>3287</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -979,37 +979,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>6809 E</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Stevens Creek - Hooks 115kV/LR Plumb Branch 46kV Rebuilds</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>20793</v>
+        <v>17993</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2033-06-01</t>
+          <t>2034-12-31</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>27.014</v>
+        <v>23.362</v>
       </c>
       <c r="H12" t="n">
-        <v>16.79</v>
+        <v>14.52</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1979</v>
+        <v>3652</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
@@ -1028,37 +1028,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>06810 H</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Summerville 115kV Loop: Rebuild</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2024-12-31</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>20794</v>
+        <v>20873</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
+          <t>GTC: BONAIRE PRIMARY 500/230KV XFMR REPLCMNT &amp; RELAY MOD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2033-06-01</t>
+          <t>2028-06-01</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>27.014</v>
+        <v>24.417</v>
       </c>
       <c r="H13" t="n">
-        <v>16.79</v>
+        <v>15.17</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1979</v>
+        <v>1248</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
@@ -1077,17 +1077,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6810 O</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1115,7 +1115,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>2485</v>
+        <v>1979</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -1126,17 +1126,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6810 O</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2027-12-31</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1164,7 +1164,7 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>2485</v>
+        <v>1979</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -1175,37 +1175,37 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>6810 O</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2027-12-31</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>17993</v>
+        <v>20793</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #5 115KV REBUILD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2034-12-31</t>
+          <t>2033-06-01</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>36.229</v>
+        <v>27.014</v>
       </c>
       <c r="H16" t="n">
-        <v>22.51</v>
+        <v>16.79</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1213,7 +1213,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>2557</v>
+        <v>2485</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -1238,23 +1238,23 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>17993</v>
+        <v>20794</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
+          <t>EVANS PRIMARY - THURMOND DAM (USA) #6 115KV REBUILD</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2034-12-31</t>
+          <t>2033-06-01</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>36.229</v>
+        <v>27.014</v>
       </c>
       <c r="H17" t="n">
-        <v>22.51</v>
+        <v>16.79</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3063</v>
+        <v>2485</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>
@@ -1273,47 +1273,929 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>21073</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>GTC: BIG SMARR - TOMOCHICHI 500KV</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2030-06-01</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>28.469</v>
+      </c>
+      <c r="H18" t="n">
+        <v>17.69</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1826</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>20067</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>SAV: DEPTFORD - MAGNOLIA 115KV RECONDUCTOR</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>29.141</v>
+      </c>
+      <c r="H19" t="n">
+        <v>18.11</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>20066</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>SAV: BOULEVARD - DEPTFORD 115KV RECONDUCTOR</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>30.419</v>
+      </c>
+      <c r="H20" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>365</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>06367 D - G</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>Jasper – Okatie 230 kV #2: Construct</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="D18" t="n">
+      <c r="D21" t="n">
+        <v>20783</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>SAV: COLEMAN - DEAN FOREST 115KV LINE REBUILD</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2028-06-01</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>31.068</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>883</v>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>21023</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>SAV: DEAN FOREST - LITTLE OGEECHEE 230 KV REBUILD</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>31.068</v>
+      </c>
+      <c r="H22" t="n">
+        <v>19.3</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1248</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>21073</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GTC: BIG SMARR - TOMOCHICHI 500KV</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2030-06-01</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>31.212</v>
+      </c>
+      <c r="H23" t="n">
+        <v>19.39</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1613</v>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>20796</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>SAV: MELDRIM BANK D REPLACEMENT</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2033-06-01</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>32.154</v>
+      </c>
+      <c r="H24" t="n">
+        <v>19.98</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2709</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>20989</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>SAV: RICE HOPE NEW AUTO TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>33.349</v>
+      </c>
+      <c r="H25" t="n">
+        <v>20.72</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>1461</v>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>20066</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>SAV: BOULEVARD - DEPTFORD 115KV RECONDUCTOR</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>33.839</v>
+      </c>
+      <c r="H26" t="n">
+        <v>21.03</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>152</v>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>06810 H</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Summerville 115kV Loop: Rebuild</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>18679</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>DU: EAST DALTON - OOSTANAULA 115KV REBUILD</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>34.813</v>
+      </c>
+      <c r="H27" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>517</v>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>21006</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>SAV: BOULEVARD - MAGNOLIA 115 KV LINE REBUILD</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>34.814</v>
+      </c>
+      <c r="H28" t="n">
+        <v>21.63</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1461</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>20067</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>SAV: DEPTFORD - MAGNOLIA 115KV RECONDUCTOR</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>35.177</v>
+      </c>
+      <c r="H29" t="n">
+        <v>21.86</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>213</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0139 M,N</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Okatie 230-115kV Substation, Jasper – Yemassee 230kV #1 Fold-in</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>2024-12-31</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>20989</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>SAV: RICE HOPE NEW AUTO TRANSFORMER</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>35.198</v>
+      </c>
+      <c r="H30" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1613</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>21006</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>SAV: BOULEVARD - MAGNOLIA 115 KV LINE REBUILD</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="H31" t="n">
+        <v>21.87</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1248</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>20783</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>SAV: COLEMAN - DEAN FOREST 115KV LINE REBUILD</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2028-06-01</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>35.769</v>
+      </c>
+      <c r="H32" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1096</v>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>6808 S</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Okatie-Bluffton 115kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>21023</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>SAV: DEAN FOREST - LITTLE OGEECHEE 230 KV REBUILD</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2029-06-01</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>35.769</v>
+      </c>
+      <c r="H33" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1461</v>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>6810 O</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Urquhart – Aiken PSA 46 kV: Rebuild</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>2027-12-31</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>17993</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2034-12-31</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>36.229</v>
+      </c>
+      <c r="H34" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>2557</v>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>6852</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Urquhart – Toolebeck 115kV line: Rebuild</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>17993</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>EVANS PRIMARY - THOMSON PRIMARY 115KV REBUILD</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2034-12-31</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>36.229</v>
+      </c>
+      <c r="H35" t="n">
+        <v>22.51</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>3063</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>06367 D - G</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Jasper – Okatie 230 kV #2: Construct</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
         <v>20175</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>CC - PROJECT CHRONOS- SK/HYUNDAI</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G36" t="n">
         <v>38.142</v>
       </c>
-      <c r="H18" t="n">
+      <c r="H36" t="n">
         <v>23.7</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Under 40 km -- can share crews &amp; equipment</t>
-        </is>
-      </c>
-      <c r="J18" t="n">
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Under 40 km -- can share crews &amp; equipment</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
